--- a/artfynd/A 20299-2026 artfynd.xlsx
+++ b/artfynd/A 20299-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,39 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>114569266</v>
+        <v>114571627</v>
       </c>
       <c r="B2" t="n">
-        <v>96604</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221944</v>
+        <v>5966</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lopplummer (aggregat)</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Huperzia selago agg.</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -715,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>573335</v>
+        <v>573203</v>
       </c>
       <c r="R2" t="n">
-        <v>6764871</v>
+        <v>6764801</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -771,10 +769,108 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
+          <t>Anna-Lotta Hellqvist</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>114569266</v>
+      </c>
+      <c r="B3" t="n">
+        <v>97977</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>221944</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Lopplummer (aggregat)</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Fallviken-Grönviken, Gstr</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>573335</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6764871</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Ockelbo</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Ockelbo</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2023-09-25</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2023-09-25</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Mårten Nilsson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
           <t>Ward Tamsyn</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
